--- a/AISE_PRD/PRD/20260907 数据统计/数据统计指标清单.xlsx
+++ b/AISE_PRD/PRD/20260907 数据统计/数据统计指标清单.xlsx
@@ -10,7 +10,7 @@
     <sheet name="数据统计指标清单" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'数据统计指标清单'!$A$1:$H$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'数据统计指标清单'!$A$1:$H$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -539,7 +539,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>按渠道、分组、活动维度统计的报名人数与报名单量</t>
+          <t>按活动、分组、测评维度统计的报名人数与报名单量；渠道为横切维度（渠道×测评关联矩阵）</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>各状态报名量与占比。标准报名：待支付/已支付/已退款；定制报名（元创S营类）：审核中/已通过/已驳回（仅特定渠道活动启用）</t>
+          <t>各状态报名量与占比。订单状态：待支付/已支付/已退款；信息状态：待审核/已通过/已驳回（首次报名信息人工审核，随 20260911 报名信息审核闭环落地）；定制报名（元创S营类）：审核中/已通过/已驳回</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>证件照审核+身份信息变更审核：待审核量、已审核量、平均审核时长；两类审核都在 admin 25 用户信息审核工作台处理（按渠道/审核类型筛选、批量审批）；标准报名无报名准入审核</t>
+          <t>首次报名信息审核+照片审核（admin 11 报名管理行内操作）+报名后信息修改审核（admin 25）：待审核量、已审核量、平均审核时长；待审期间新提交覆盖旧工单（旧单「已作废」）；照片审核自 25 回归 11（随 20260911 方案落地，待确认稿）</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>首笔待审材料提交（照片/身份信息变更）</t>
+          <t>首笔待审材料提交（首次报名信息/照片）</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>本活动审核全部完成</t>
+          <t>本测评审核全部完成</t>
         </is>
       </c>
     </row>
@@ -702,12 +702,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>渠道分布</t>
+          <t>活动分布</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>各渠道报名量；与分组分布、活动分布联动下钻：渠道 → 分组 → 活动；客户视角自动限定本组织</t>
+          <t>各活动的报名量（活动=时间段内一组测评，20260908/20260912 新实体）</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>渠道内各分组的报名量；依赖渠道设置分组（渠道→分组→活动层级）；未分组活动归「其他」</t>
+          <t>活动内各分组的报名量（分组挂活动下、全渠道一致，20260912 V3；未分组测评归「未分组」）</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>活动分布</t>
+          <t>测评分布</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>各活动的报名量（一个活动对应一场考试）；与渠道、分组分布联动下钻</t>
+          <t>各场测评的报名量（一场测评对应爱测评一场测评，统计原子）；支持 活动→分组→测评 逐级下钻</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -828,79 +828,79 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
+          <t>渠道分布</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>各渠道的报名量（渠道×测评矩阵关联）；管理员看全渠道、客户即本渠道视角；支持按报名可见性（正常/隐藏报名，20260910）筛选</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>柱状图+表格</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>首笔报名产生</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>事件驱动（报名落库即更新）</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>报名截止</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>考前（报名）</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
           <t>费用概览</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>报名费收款/退款金额概览；明细与多维分析跳转交易数据统计（admin 30）；对客户默认关闭、按组织数据权限放开</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>元</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>指标卡片</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>首笔支付成功</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>事件驱动（支付/退款落库即更新）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>退款通道关闭</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>开考后（模拟考）</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>模拟考参与率</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>进入过模拟考的考生（含未完成）÷ 已报名考生；未进入模拟考人数单列展示</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>指标卡片</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>模拟考开启且首名考生进入</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>事件驱动</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>模拟考关闭</t>
         </is>
       </c>
     </row>
@@ -912,79 +912,79 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
+          <t>模拟考参与率</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>进入过模拟考的学员（含未完成）÷ 已报名学员；未进入模拟考人数单列展示</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>指标卡片</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>模拟考开启且首名学员进入</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>事件驱动</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>模拟考关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>开考后（模拟考）</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
           <t>模拟考完成情况</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>参与人数、完成人次、人均参加次数</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>参与人数、完成人次、人均参加次数（模拟考次数限制 N 次/无限次，20260912 V3）</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>人/人次/次</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>指标卡片+表格</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>模拟考开启且首名考生完成</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>模拟考开启且首名学员完成</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>事件驱动</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>模拟考关闭</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>开考后（考前环节）</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>到场数据</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>应考人数、实际到场人数、到场率、未到场人数</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>人/%</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>指标卡片</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>正式考开考（首位考生进入）</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>每分钟（可放宽至5分钟）</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>考试结束（数据冻结）</t>
         </is>
       </c>
     </row>
@@ -996,27 +996,27 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>身份校验情况</t>
+          <t>到场数据</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>校验通过/校验未通过/未校验；检录配置为「不开启」时计入未启用、排除在分母外</t>
+          <t>应考人数、实际到场人数、到场率、未到场人数</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>人</t>
+          <t>人/%</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>堆叠柱状图+表格</t>
+          <t>指标卡片</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>检录环节开启（开考前）</t>
+          <t>正式考开考（首位学员进入）</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>考试结束（数据冻结）</t>
+          <t>测评结束（数据冻结）</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>录屏开启情况</t>
+          <t>身份校验情况</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>已开启/未开启/开启异常</t>
+          <t>校验通过/校验未通过/未校验；检录配置为「不开启」时计入未启用、排除在分母外</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1053,12 +1053,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>环形图+表格</t>
+          <t>堆叠柱状图+表格</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>考生进入考试并开始接入监考</t>
+          <t>检录环节开启（开考前）</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>考试结束（监考类数据展示「-」）</t>
+          <t>测评结束（数据冻结）</t>
         </is>
       </c>
     </row>
@@ -1080,27 +1080,27 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>设备检测完成情况</t>
+          <t>录屏开启情况</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>摄像头、麦克风等设备检测完成率</t>
+          <t>已开启/未开启/开启异常</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>人/%</t>
+          <t>人</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>指标卡片</t>
+          <t>环形图+表格</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>设备检测页开放（考前）</t>
+          <t>学员进入测评并开始接入监考</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>考试结束（数据冻结）</t>
+          <t>测评结束（监考类数据展示「-」）</t>
         </is>
       </c>
     </row>
@@ -1122,79 +1122,79 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>设备检测完成情况</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>摄像头、麦克风等设备检测完成率</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>人/%</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>指标卡片</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>设备检测页开放（考前）</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>每分钟（可放宽至5分钟）</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>测评结束（数据冻结）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>开考后（考前环节）</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
           <t>检录提交情况</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>检录照片/视频已提交量（检录按考试配置为强制/非强制/不开启三态）</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>检录照片/视频已提交量（检录按测评配置为强制/非强制/不开启三态）</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>指标卡片</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>检录环节开启</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>每分钟（可放宽至5分钟）</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>考试结束（数据冻结）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>考中</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>进行中人数</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>已进入测评（开始后进入过即算，含当前在场与不在场）且未交卷的考生总数</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>人</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>指标卡片</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>正式考开考（开考前显示「-」）</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>每分钟（可放宽至5分钟）</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>考试结束（数据冻结）</t>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>测评结束（数据冻结）</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>在线人数</t>
+          <t>进行中人数</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>当前在线的考生数量</t>
+          <t>已进入测评（开始后进入过即算，含当前在场与不在场）且未交卷的学员总数</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>考试结束（展示「-」）</t>
+          <t>测评结束（数据冻结）</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>已交卷人数</t>
+          <t>在线人数</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>已交卷的考生总数</t>
+          <t>当前在线的学员数量</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>首份交卷产生</t>
+          <t>正式考开考（开考前显示「-」）</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>考试结束（数据冻结）</t>
+          <t>测评结束（展示「-」）</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>未进入人数</t>
+          <t>已交卷人数</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>已报名但从未进入本测评的考生总数</t>
+          <t>已交卷的学员总数</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>正式考开考</t>
+          <t>首份交卷产生</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>考试结束（数据冻结）</t>
+          <t>测评结束（数据冻结）</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>监考接入分布</t>
+          <t>未进入人数</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>当前在线考生中：摄像头+录屏/仅摄像头/仅录屏/未接入；AISE 手机监考纳入接入状态统计</t>
+          <t>已报名但从未进入本测评的学员总数</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>堆叠条形图+表格</t>
+          <t>指标卡片</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>开考且首名考生在线</t>
+          <t>正式考开考</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>考试结束（展示「-」）</t>
+          <t>测评结束（数据冻结）</t>
         </is>
       </c>
     </row>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>作答状态-时间变化图</t>
+          <t>监考接入分布</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>以开考时间为起点至结束每10分钟一段，统计（当前段，当前段-10min]内已完成/进行中/缺考考生数</t>
+          <t>当前在线学员中：摄像头+录屏/仅摄像头/仅录屏/未接入；手机监考（监考8项之一，20260912 V3）纳入接入状态统计</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1389,22 +1389,22 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>折线图（三系列）</t>
+          <t>堆叠条形图+表格</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>开考后首个10分钟采样点</t>
+          <t>开考且首名学员在线</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>每10分钟（基于每分钟采样聚合）</t>
+          <t>每分钟（可放宽至5分钟）</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>考试结束（曲线定格）</t>
+          <t>测评结束（展示「-」）</t>
         </is>
       </c>
     </row>
@@ -1416,27 +1416,27 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>作答率-时间变化图</t>
+          <t>作答状态-时间变化图</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>已参测学生的已作答题目数÷（题目总数×参测学生总数）；已作答标准=题目无空白答案</t>
+          <t>以开测时间为起点至结束每10分钟一段，统计（当前段，当前段-10min]内已完成/进行中/缺考学员数</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>人</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>折线图</t>
+          <t>折线图（三系列）</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>开考后首个10分钟采样点</t>
+          <t>开测后首个10分钟采样点</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>考试结束（曲线定格）</t>
+          <t>测评结束（曲线定格）</t>
         </is>
       </c>
     </row>
@@ -1458,79 +1458,79 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>作答率-时间变化图</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>已参测学员的已作答题目数÷（题目总数×参测学员总数）；已作答标准=题目无空白答案</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>折线图</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>开测后首个10分钟采样点</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>每10分钟（基于每分钟采样聚合）</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>测评结束（曲线定格）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>考中</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
           <t>考中异常</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>切屏人数与次数、摄像头异常人数（数据来源为考生监控已有记录）</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>人/次</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>切屏人数与次数、摄像头异常人数、多IP同时在线人数/人次（同一学员同一时段多IP登录答题，20260911 P13 增补；监控卡片加多IP标记，本期只做可见）</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>人/次/人次</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>指标卡片+表格</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>正式考开考</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>每分钟（可放宽至5分钟）</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>考试结束（数据冻结）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>考后</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>交卷时间分布</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>从0到最大交卷时间每10min分档（档位对应(0,10min]）的档内人数；配套平均交卷时间、最快交卷时间</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>人/分钟</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>柱状图+指标卡片</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>首份交卷产生</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>事件驱动（交卷落库即更新）</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>考试结束（全员交卷完成）</t>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>测评结束（数据冻结）</t>
         </is>
       </c>
     </row>
@@ -1542,37 +1542,37 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>批改进度</t>
+          <t>交卷时间分布</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>待批改/批改中（已批试卷数/总试卷数）/已完成量与占比；含平均批改时长</t>
+          <t>从0到最大交卷时间每10min分档（档位对应(0,10min]）的档内人数；配套平均交卷时间、最快交卷时间</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>份/%</t>
+          <t>人/分钟</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>进度条+表格</t>
+          <t>柱状图+指标卡片</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>考试结束进入批改</t>
+          <t>首份交卷产生</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>事件驱动（异步批改任务推进）</t>
+          <t>事件驱动（交卷落库即更新）</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>全部试卷批改完成（重新批改时刷新）</t>
+          <t>测评结束（全员交卷完成）</t>
         </is>
       </c>
     </row>
@@ -1584,37 +1584,37 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>成绩统计</t>
+          <t>批改进度</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>平均分、最高/最低分、分数段分布、达标率、等级分布；ABCD口径：100分制 A:90-100/B:60-89/C:45-59/D:45以下，非100分制等比例换算</t>
+          <t>待批改/批改中（已批试卷数/总试卷数）/已完成量与占比；含平均批改时长</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>分/%</t>
+          <t>份/%</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>指标卡片+柱状图+饼图</t>
+          <t>进度条+表格</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>成绩发布</t>
+          <t>测评结束进入批改</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>成绩发布时生成；成绩复核更正时更新</t>
+          <t>事件驱动（异步批改任务推进）</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>成绩复核期结束（最终成绩确认）</t>
+          <t>全部试卷批改完成（重新批改时刷新）</t>
         </is>
       </c>
     </row>
@@ -1626,37 +1626,37 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>报告生成进度</t>
+          <t>成绩统计</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>已生成/生成中/未开始/失败；生成时机为成绩发布后自动触发（异步任务）</t>
+          <t>平均分、最高/最低分、分数段分布、达标率、等级分布；等级口径=该测评证书分数线规则（按分数/按比例划线，档位名可自定义如一等奖，20260909），未配置走固定映射表兜底；达标=达到勾选「发放证书」最低档</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>份/%</t>
+          <t>分/%</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>进度条+表格</t>
+          <t>指标卡片+柱状图+饼图</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>成绩发布（生成任务触发）</t>
+          <t>成绩发布</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>事件驱动（异步任务推进，分钟级）</t>
+          <t>成绩发布时生成；成绩复核更正时更新</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>全部到达终态（已生成或失败）</t>
+          <t>成绩复核期结束（最终成绩确认）</t>
         </is>
       </c>
     </row>
@@ -1668,12 +1668,12 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>证书生成进度（电子）</t>
+          <t>报告生成进度</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>等待成绩/生成中/待签发/已签发/失败，对齐电子证书签发状态链路（仅覆盖达标考生）</t>
+          <t>已生成/生成中/未开始/失败；生成时机为成绩发布后自动触发（异步任务）；报告等级按生成时点的配置计算，配置修改不溯及已生成报告</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -1688,17 +1688,17 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>成绩发布（进入生成队列）</t>
+          <t>成绩发布（生成任务触发）</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>事件驱动（异步任务+签发中心推进）</t>
+          <t>事件驱动（异步任务推进，分钟级）</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>全部到达终态（已签发或失败）</t>
+          <t>全部到达终态（已生成或失败）</t>
         </is>
       </c>
     </row>
@@ -1710,210 +1710,252 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
+          <t>证书生成进度（电子）</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>等待成绩/生成中/待签发/已签发/失败，对齐电子证书签发状态链路（仅覆盖达标学员）</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>份/%</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>进度条+表格</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>成绩发布（进入生成队列）</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>事件驱动（异步任务+签发中心推进）</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>全部到达终态（已签发或失败）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>考后</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
           <t>证书制作进度（实体）</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>待复核/公示/制作中/已寄送各环节数量，对齐实体证书生命周期</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>份</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>阶段进度条+表格</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>批改完成进入复核环节</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>事件驱动（人工环节推进）</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>全部已寄送</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>考中/考后（明细）</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>成绩列表（按人）</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>全量考生列表：考生信息、起止时间、作答时长、跳出次数、考试状态（已交卷/进行中/未进入）、批改状态（未批改/批改中/最近批改分数）</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>全量学员列表：学员信息、起止时间、作答时长、跳出次数、测评状态（已交卷/进行中/未进入）、批改状态（未批改/批改中/最近批改分数）；按学员跨测评查询由 20260911 学员答卷查询（P10）单独承载</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>表格</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>首名考生进入考试（考中即可见）</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>首名学员进入测评（考中即可见）</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>考中每分钟；考后事件驱动</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>批改完成后冻结（重新批改时刷新）</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>考后（明细）</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>题目统计（按题）</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>客观题（单选/多选/判断）=正确答案选择率；填空题=满分占比+各空得分率；主观/编程/实践题=满分占比+平均得分率+作答率</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>表格+条形图</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>考试结束且批改完成（此前显示「请等待考试结束、批改完成」）</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>测评结束且批改完成（此前显示「请等待测评结束、批改完成」）</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>批改完成时生成</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>批改完成后冻结（重新批改时刷新）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>考中（明细）</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>逐题作答热力矩阵</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>每题已作答人数÷参测人数；四色分档 0-45%/45-60%/60-90%/90-100%</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>热力矩阵</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>正式考开考</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>每分钟（可放宽至5分钟）</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>考试结束（定格）</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
+          <t>考中（明细）</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>逐题作答热力矩阵</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>每题已作答人数÷参测人数；四色分档 0-45%/45-60%/60-90%/90-100%</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>热力矩阵</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>正式考开考</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>每分钟（可放宽至5分钟）</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>测评结束（定格）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
           <t>考中/考后（明细）</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>查看试卷</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>只读试卷详情：考生名称、考生得分、限时时长、试卷总分；每题展示正确答案/考生答案/考生得分；未作答显示「-」、未批改显示「暂未批改」</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>只读试卷详情：学员名称、学员得分、限时时长、试卷总分；每题展示正确答案/学员答案/学员得分；未作答显示「-」、未批改显示「暂未批改」</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>详情页</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>首名考生开始作答（考中实时可看已完成部分）</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>首名学员开始作答（考中实时可看已完成部分）</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>随作答保存实时更新；批改完成后补齐分数</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>考试结束（作答内容定格，批改分数随后补齐）</t>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>测评结束（作答内容定格，批改分数随后补齐）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H34"/>
+  <autoFilter ref="A1:H35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/AISE_PRD/PRD/20260907 数据统计/数据统计指标清单.xlsx
+++ b/AISE_PRD/PRD/20260907 数据统计/数据统计指标清单.xlsx
@@ -10,7 +10,7 @@
     <sheet name="数据统计指标清单" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'数据统计指标清单'!$A$1:$H$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'数据统计指标清单'!$A$7:$H$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,7 +30,7 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="11.5"/>
     </font>
     <font>
       <b val="1"/>
@@ -39,13 +39,23 @@
     <font>
       <sz val="10.5"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8EEF9"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -89,21 +99,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -471,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -484,1478 +503,1520 @@
     <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>统计范围与筛选定义（适用于下表几乎全部数据项）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>几乎所有数据项都可通过筛选确定统计范围，层级为：活动 → 分组 → 测评；渠道为横切维度（任意层级均可按渠道拆分查看；客户视角渠道维度锁定本渠道）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>活动（最大颗粒度）：查看一个活动的整体数据，也可以查看各渠道的数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>分组（活动下）：可筛选多个分组，分别查看每个分组的整组数据，也可以查看各渠道的数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>测评（分组下，最小颗粒度）：可筛选多个测评，分别查看每个测评的数据，也可以查看各渠道的数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
           <t>阶段</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>数据项</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>数据口径</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>建议显示样式</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>数据可见的起点</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>数据更新周期</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>数据停止更新的时间点</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>考前（报名）</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>报名人数/报名单量</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>按活动、分组、测评维度统计的报名人数与报名单量；渠道为横切维度（渠道×测评关联矩阵）</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>人/单</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>指标卡片+表格</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>报名开启后产生首笔报名</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>事件驱动（报名落库即更新）</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>报名截止</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>考前（报名）</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>每日新增报名趋势</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>按自然日累计的新增报名量</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>人/日</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>折线图</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>报名开启后首个数据日</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>每日汇总（随报名累计）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>报名截止</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>考前（报名）</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>报名状态分布</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>各状态报名量与占比。订单状态：待支付/已支付/已退款；信息状态：待审核/已通过/已驳回（首次报名信息人工审核，随 20260911 报名信息审核闭环落地）；定制报名（元创S营类）：审核中/已通过/已驳回</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>单/%</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>环形图+表格</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>首笔报名产生</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>事件驱动（状态流转即更新）</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>退款通道关闭（状态最终冻结）</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>考前（报名）</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>审核进展</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>首次报名信息审核+照片审核（admin 11 报名管理行内操作）+报名后信息修改审核（admin 25）：待审核量、已审核量、平均审核时长；待审期间新提交覆盖旧工单（旧单「已作废」）；照片审核自 25 回归 11（随 20260911 方案落地，待确认稿）</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>单/小时</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>指标卡片+表格</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>首笔待审材料提交（首次报名信息/照片）</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>事件驱动（审核动作落库即更新）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>本测评审核全部完成</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>考前（报名）</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>活动分布</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>各活动的报名量（活动=时间段内一组测评，20260908/20260912 新实体）</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>柱状图+表格</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>首笔报名产生</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>事件驱动（报名落库即更新）</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>报名截止</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>考前（报名）</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>分组分布</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>活动内各分组的报名量（分组挂活动下、全渠道一致，20260912 V3；未分组测评归「未分组」）</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>柱状图+表格</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>首笔报名产生</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>事件驱动（报名落库即更新）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>报名截止</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>考前（报名）</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>测评分布</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>各场测评的报名量（一场测评对应爱测评一场测评，统计原子）；支持 活动→分组→测评 逐级下钻</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>柱状图+表格</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>首笔报名产生</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>事件驱动（报名落库即更新）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>报名截止</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>考前（报名）</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>渠道分布</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>各渠道的报名量（渠道×测评矩阵关联）；管理员看全渠道、客户即本渠道视角；支持按报名可见性（正常/隐藏报名，20260910）筛选</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>柱状图+表格</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>首笔报名产生</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>事件驱动（报名落库即更新）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>报名截止</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>考前（报名）</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>费用概览</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>报名费收款/退款金额概览；明细与多维分析跳转交易数据统计（admin 30）；对客户默认关闭、按组织数据权限放开</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>元</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>指标卡片</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>首笔支付成功</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>事件驱动（支付/退款落库即更新）</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>退款通道关闭</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>开考后（模拟考）</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>模拟考参与率</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>进入过模拟考的学员（含未完成）÷ 已报名学员；未进入模拟考人数单列展示</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>指标卡片</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>模拟考开启且首名学员进入</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>事件驱动</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>模拟考关闭</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>开考后（模拟考）</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>模拟考完成情况</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>参与人数、完成人次、人均参加次数（模拟考次数限制 N 次/无限次，20260912 V3）</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>人/人次/次</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>指标卡片+表格</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>模拟考开启且首名学员完成</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>事件驱动</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>模拟考关闭</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>开考后（考前环节）</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>到场数据</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>应考人数、实际到场人数、到场率、未到场人数</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>人/%</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>指标卡片</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>正式考开考（首位学员进入）</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>每分钟（可放宽至5分钟）</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>测评结束（数据冻结）</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>开考后（考前环节）</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>身份校验情况</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>校验通过/校验未通过/未校验；检录配置为「不开启」时计入未启用、排除在分母外</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>堆叠柱状图+表格</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>检录环节开启（开考前）</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>每分钟（可放宽至5分钟）</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>测评结束（数据冻结）</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>开考后（考前环节）</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>录屏开启情况</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>已开启/未开启/开启异常</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>环形图+表格</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>学员进入测评并开始接入监考</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>每分钟（可放宽至5分钟）</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>测评结束（监考类数据展示「-」）</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>开考后（考前环节）</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>设备检测完成情况</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>摄像头、麦克风等设备检测完成率</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>人/%</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>指标卡片</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>设备检测页开放（考前）</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>每分钟（可放宽至5分钟）</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>测评结束（数据冻结）</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>开考后（考前环节）</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>检录提交情况</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>检录照片/视频已提交量（检录按测评配置为强制/非强制/不开启三态）</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>指标卡片</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>检录环节开启</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>每分钟（可放宽至5分钟）</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>测评结束（数据冻结）</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>考中</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>进行中人数</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>已进入测评（开始后进入过即算，含当前在场与不在场）且未交卷的学员总数</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>指标卡片</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>正式考开考（开考前显示「-」）</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>每分钟（可放宽至5分钟）</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>测评结束（数据冻结）</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>考中</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>在线人数</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>当前在线的学员数量</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>指标卡片</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>正式考开考（开考前显示「-」）</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>每分钟（可放宽至5分钟）</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>测评结束（展示「-」）</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>考中</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>已交卷人数</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>已交卷的学员总数</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>指标卡片</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>首份交卷产生</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>每分钟（可放宽至5分钟）</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>测评结束（数据冻结）</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>考中</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>未进入人数</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>已报名但从未进入本测评的学员总数</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>指标卡片</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>正式考开考</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>每分钟（可放宽至5分钟）</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>测评结束（数据冻结）</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>考中</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>监考接入分布</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>当前在线学员中：摄像头+录屏/仅摄像头/仅录屏/未接入；手机监考（监考8项之一，20260912 V3）纳入接入状态统计</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>堆叠条形图+表格</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>开考且首名学员在线</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>每分钟（可放宽至5分钟）</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>测评结束（展示「-」）</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>考中</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>作答状态-时间变化图</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>以开测时间为起点至结束每10分钟一段，统计（当前段，当前段-10min]内已完成/进行中/缺考学员数</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>折线图（三系列）</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>开测后首个10分钟采样点</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>每10分钟（基于每分钟采样聚合）</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>测评结束（曲线定格）</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>考中</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>作答率-时间变化图</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>已参测学员的已作答题目数÷（题目总数×参测学员总数）；已作答标准=题目无空白答案</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>折线图</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>开测后首个10分钟采样点</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>每10分钟（基于每分钟采样聚合）</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>测评结束（曲线定格）</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>考中</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>考中异常</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>切屏人数与次数、摄像头异常人数、多IP同时在线人数/人次（同一学员同一时段多IP登录答题，20260911 P13 增补；监控卡片加多IP标记，本期只做可见）</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>人/次/人次</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>指标卡片+表格</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>正式考开考</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>每分钟（可放宽至5分钟）</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>测评结束（数据冻结）</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>考后</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>交卷时间分布</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>从0到最大交卷时间每10min分档（档位对应(0,10min]）的档内人数；配套平均交卷时间、最快交卷时间</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>人/分钟</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>柱状图+指标卡片</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>首份交卷产生</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>事件驱动（交卷落库即更新）</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>测评结束（全员交卷完成）</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>考后</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>批改进度</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>待批改/批改中（已批试卷数/总试卷数）/已完成量与占比；含平均批改时长</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>份/%</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>进度条+表格</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>测评结束进入批改</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>事件驱动（异步批改任务推进）</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>全部试卷批改完成（重新批改时刷新）</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>考后</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>成绩统计</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>平均分、最高/最低分、分数段分布、达标率、等级分布；等级口径=该测评证书分数线规则（按分数/按比例划线，档位名可自定义如一等奖，20260909），未配置走固定映射表兜底；达标=达到勾选「发放证书」最低档</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>分/%</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>指标卡片+柱状图+饼图</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>成绩发布</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>成绩发布时生成；成绩复核更正时更新</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>成绩复核期结束（最终成绩确认）</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>考后</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>报告生成进度</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>已生成/生成中/未开始/失败；生成时机为成绩发布后自动触发（异步任务）；报告等级按生成时点的配置计算，配置修改不溯及已生成报告</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>份/%</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>进度条+表格</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>成绩发布（生成任务触发）</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>事件驱动（异步任务推进，分钟级）</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>全部到达终态（已生成或失败）</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>考后</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>证书生成进度（电子）</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>等待成绩/生成中/待签发/已签发/失败，对齐电子证书签发状态链路（仅覆盖达标学员）</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>份/%</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>进度条+表格</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>成绩发布（进入生成队列）</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>事件驱动（异步任务+签发中心推进）</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>全部到达终态（已签发或失败）</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>考后</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>证书制作进度（实体）</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>待复核/公示/制作中/已寄送各环节数量，对齐实体证书生命周期</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>份</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>阶段进度条+表格</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>批改完成进入复核环节</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>事件驱动（人工环节推进）</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>全部已寄送</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>考中/考后（明细）</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>成绩列表（按人）</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>全量学员列表：学员信息、起止时间、作答时长、跳出次数、测评状态（已交卷/进行中/未进入）、批改状态（未批改/批改中/最近批改分数）；按学员跨测评查询由 20260911 学员答卷查询（P10）单独承载</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>表格</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>首名学员进入测评（考中即可见）</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t>考中每分钟；考后事件驱动</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t>批改完成后冻结（重新批改时刷新）</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>考后（明细）</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>题目统计（按题）</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>客观题（单选/多选/判断）=正确答案选择率；填空题=满分占比+各空得分率；主观/编程/实践题=满分占比+平均得分率+作答率</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>表格+条形图</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>测评结束且批改完成（此前显示「请等待测评结束、批改完成」）</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>批改完成时生成</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>批改完成后冻结（重新批改时刷新）</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>考中（明细）</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>逐题作答热力矩阵</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>每题已作答人数÷参测人数；四色分档 0-45%/45-60%/60-90%/90-100%</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>热力矩阵</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t>正式考开考</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>每分钟（可放宽至5分钟）</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>测评结束（定格）</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>考中/考后（明细）</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>查看试卷</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>只读试卷详情：学员名称、学员得分、限时时长、试卷总分；每题展示正确答案/学员答案/学员得分；未作答显示「-」、未批改显示「暂未批改」</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>详情页</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t>首名学员开始作答（考中实时可看已完成部分）</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>随作答保存实时更新；批改完成后补齐分数</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>测评结束（作答内容定格，批改分数随后补齐）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H35"/>
+  <autoFilter ref="A7:H41"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:H5"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/AISE_PRD/PRD/20260907 数据统计/数据统计指标清单.xlsx
+++ b/AISE_PRD/PRD/20260907 数据统计/数据统计指标清单.xlsx
@@ -588,12 +588,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>报名人数/报名单量</t>
+          <t>报名总人数/总单量</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>按活动、分组、测评维度统计的报名人数与报名单量；渠道为横切维度（渠道×测评关联矩阵）</t>
+          <t>整体：筛选范围内报名总人数与总单量；每日：按自然日的新增报名人数与单量（含累计）；层级筛选（活动/分组/测评）与渠道横切适用</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>指标卡片+表格</t>
+          <t>指标卡片（整体）+折线图/表格（每日）</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>事件驱动（报名落库即更新）</t>
+          <t>事件驱动（报名落库即更新），每日视图按日汇总</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -630,32 +630,32 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>每日新增报名趋势</t>
+          <t>按支付方式统计</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>按自然日累计的新增报名量</t>
+          <t>各支付方式的报名人数与单量（现阶段微信支付，后续新增支付方式自动纳入维度）；支持整体统计与每日统计</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>人/日</t>
+          <t>人/单</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>折线图</t>
+          <t>饼图+表格（整体）、堆叠柱状图（每日）</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>报名开启后首个数据日</t>
+          <t>首笔支付行为产生</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>每日汇总（随报名累计）</t>
+          <t>事件驱动（支付落库即更新）</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -672,22 +672,22 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>报名状态分布</t>
+          <t>按支付状态统计</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>各状态报名量与占比。订单状态：待支付/已支付/已退款；信息状态：待审核/已通过/已驳回（首次报名信息人工审核，随 20260911 报名信息审核闭环落地）；定制报名（元创S营类）：审核中/已通过/已驳回</t>
+          <t>各支付状态的报名人数与单量：待支付/已支付/已退款；支持整体统计与每日统计</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>单/%</t>
+          <t>人/单</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>环形图+表格</t>
+          <t>环形图+表格（整体）、堆叠柱状图（每日）</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -714,27 +714,27 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>审核进展</t>
+          <t>审核数据</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>首次报名信息审核+照片审核（admin 11 报名管理行内操作）+报名后信息修改审核（admin 25）：待审核量、已审核量、平均审核时长；待审期间新提交覆盖旧工单（旧单「已作废」）；照片审核自 25 回归 11（随 20260911 方案落地，待确认稿）</t>
+          <t>每日：当日通过数量、不通过（驳回）数量、日末待审核存量；整体：累计通过、累计不通过、当前待审核；审核源=首次报名信息+照片（admin 11 行内操作）+报名后信息修改（admin 25，随 20260911 方案落地）；定制报名沿用其审核制</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>单/小时</t>
+          <t>单</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>指标卡片+表格</t>
+          <t>柱状图+表格（每日）、指标卡片（整体）</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>首笔待审材料提交（首次报名信息/照片）</t>
+          <t>首笔待审材料提交</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">

--- a/AISE_PRD/PRD/20260907 数据统计/数据统计指标清单.xlsx
+++ b/AISE_PRD/PRD/20260907 数据统计/数据统计指标清单.xlsx
@@ -961,37 +961,37 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>开考后（模拟考）</t>
+          <t>考前（模拟考）</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>模拟考参与率</t>
+          <t>模拟考参与漏斗</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>进入过模拟考的学员（含未完成）÷ 已报名学员；未进入模拟考人数单列展示</t>
+          <t>模拟考应参人数（已报名且该测评模拟考开启的学员）、参考人数（进入过模拟考即算，含未完成）、完成人数（完成模拟考交卷）；适用全局筛选定义（活动/分组/测评 + 渠道横切）</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>人</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>指标卡片</t>
+          <t>漏斗图/指标卡片</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>模拟考开启且首名学员进入</t>
+          <t>模拟考开启（应参人数自首笔报名起可算）</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>事件驱动</t>
+          <t>事件驱动（进入/交卷落库即更新）</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -1003,42 +1003,42 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>开考后（模拟考）</t>
+          <t>考前（模拟考）</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>模拟考完成情况</t>
+          <t>模拟考监考开启率</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>参与人数、完成人次、人均参加次数（模拟考次数限制 N 次/无限次，20260912 V3）</t>
+          <t>摄像头监考开启率、录屏监考开启率、检录照片上传率三项；各分母=模拟考生效监考配置为「强制/非强制」该项的人数（「不开启」配置排除在分母外；模拟考监考可跟随正式考或自定义，20260912 V3）</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>人/人次/次</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>指标卡片+表格</t>
+          <t>进度条/环形图+表格</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>模拟考开启且首名学员完成</t>
+          <t>模拟考开启且首名学员进入</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>事件驱动</t>
+          <t>每分钟（可放宽至5分钟）</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>模拟考关闭</t>
+          <t>模拟考结束（数据冻结）</t>
         </is>
       </c>
     </row>
